--- a/Calendario-2027-1.xlsx
+++ b/Calendario-2027-1.xlsx
@@ -29,15 +29,15 @@
     <t xml:space="preserve">Unidad</t>
   </si>
   <si>
+    <t xml:space="preserve">Temas (sugeridos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Fechas</t>
   </si>
   <si>
-    <t xml:space="preserve">Temas (sugeridos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">profe</t>
-  </si>
-  <si>
     <t xml:space="preserve">Presentación Curso</t>
   </si>
   <si>
@@ -152,7 +152,7 @@
     <t xml:space="preserve">Monitoreo de fauna y ecosistemas</t>
   </si>
   <si>
-    <t xml:space="preserve">Transcriptomica</t>
+    <t xml:space="preserve">Transcriptomica y genómica</t>
   </si>
   <si>
     <t xml:space="preserve">Genómica</t>
@@ -302,52 +302,48 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -600,735 +596,727 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H48"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr defaultColWidth="9.1484375" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="35.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="37.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="47.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="30.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="23.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="35.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="37.57"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="30.29"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="23.57"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="0" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="0" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="0" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="3"/>
+      <c r="G1" s="1"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="0" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="5" t="n">
-        <v>46245</v>
-      </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="4" t="n">
+        <v>46252</v>
+      </c>
+      <c r="F2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="5" t="n">
-        <v>46246</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="B3" s="2"/>
+      <c r="C3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="D3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="5" t="n">
+        <v>46253</v>
+      </c>
+      <c r="F3" s="4"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="4"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="2" t="s">
+      <c r="B4" s="2"/>
+      <c r="C4" s="3" t="s">
         <v>9</v>
       </c>
+      <c r="F4" s="6"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="0" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="7" t="n">
-        <v>46248</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="C5" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="D5" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>46255</v>
+      </c>
+      <c r="F5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="0" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5" t="n">
-        <v>46252</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="B6" s="2"/>
+      <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="H6" s="3"/>
+      <c r="D6" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="G6" s="1"/>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="0" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="7" t="n">
-        <v>46253</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>7</v>
+      <c r="D7" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>46259</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="0" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="8" t="s">
+      <c r="B8" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="5" t="n">
-        <v>46255</v>
-      </c>
-      <c r="D8" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="D8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="3"/>
+      <c r="E8" s="4" t="n">
+        <v>46260</v>
+      </c>
+      <c r="G8" s="1"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="B9" s="8"/>
-      <c r="C9" s="7" t="n">
-        <v>46259</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="A9" s="0" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="7"/>
+      <c r="C9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="D9" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="E9" s="5" t="n">
+        <v>46262</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="0" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="8"/>
-      <c r="C10" s="5" t="n">
-        <v>46260</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="B10" s="7"/>
+      <c r="C10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="D10" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H10" s="3"/>
+      <c r="E10" s="4" t="n">
+        <v>46266</v>
+      </c>
+      <c r="G10" s="1"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="0" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="8"/>
-      <c r="C11" s="7" t="n">
-        <v>46262</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="B11" s="7"/>
+      <c r="C11" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="D11" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="E11" s="5" t="n">
+        <v>46267</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="0" t="n">
         <v>10</v>
       </c>
-      <c r="B12" s="8"/>
-      <c r="C12" s="5" t="n">
-        <v>46266</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="B12" s="7"/>
+      <c r="C12" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="D12" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="E12" s="4" t="n">
+        <v>46269</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="0" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="7" t="n">
-        <v>46267</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="B13" s="7"/>
+      <c r="C13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="D13" s="3" t="s">
         <v>16</v>
       </c>
+      <c r="E13" s="8" t="n">
+        <v>46273</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="0" t="n">
         <v>12</v>
       </c>
-      <c r="B14" s="8"/>
-      <c r="C14" s="5" t="n">
-        <v>46269</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="B14" s="7"/>
+      <c r="C14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="D14" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="E14" s="4" t="n">
+        <v>46274</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="0" t="n">
         <v>13</v>
       </c>
-      <c r="B15" s="8"/>
-      <c r="C15" s="9" t="n">
-        <v>46273</v>
-      </c>
-      <c r="D15" s="2" t="s">
+      <c r="B15" s="7"/>
+      <c r="C15" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="D15" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="E15" s="5" t="n">
+        <v>46276</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="0" t="n">
         <v>14</v>
       </c>
-      <c r="B16" s="8"/>
-      <c r="C16" s="5" t="n">
-        <v>46274</v>
-      </c>
-      <c r="D16" s="2" t="s">
+      <c r="B16" s="7"/>
+      <c r="C16" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="D16" s="3" t="s">
         <v>23</v>
       </c>
+      <c r="E16" s="4" t="n">
+        <v>46283</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="28.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="0" t="n">
         <v>15</v>
       </c>
-      <c r="B17" s="8"/>
-      <c r="C17" s="7" t="n">
-        <v>46276</v>
+      <c r="B17" s="7"/>
+      <c r="C17" s="1" t="s">
+        <v>26</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>46287</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="7"/>
+      <c r="C18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>46288</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="0" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>46290</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="0" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>46294</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="0" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="7"/>
+      <c r="C21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="0" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>46297</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="0" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="9"/>
+      <c r="C23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>46301</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="0" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="9"/>
+      <c r="C24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>46302</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="0" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="9"/>
+      <c r="C25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>46304</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="0" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="9"/>
+      <c r="C26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>46308</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="0" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="9"/>
+      <c r="C27" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>46309</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="0" t="n">
         <v>26</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="8"/>
-      <c r="C18" s="5" t="n">
-        <v>46283</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="B28" s="9"/>
+      <c r="C28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>46311</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="0" t="n">
         <v>27</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="8"/>
-      <c r="C19" s="7" t="n">
-        <v>46287</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="B29" s="9"/>
+      <c r="C29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="0" t="n">
         <v>28</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="1" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="8"/>
-      <c r="C20" s="5" t="n">
-        <v>46288</v>
-      </c>
-      <c r="D20" s="2" t="s">
+      <c r="B30" s="9"/>
+      <c r="C30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>46315</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="0" t="n">
         <v>29</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="8"/>
-      <c r="C21" s="7" t="n">
-        <v>46290</v>
-      </c>
-      <c r="D21" s="2" t="s">
+      <c r="B31" s="9"/>
+      <c r="C31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>46316</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="0" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="9"/>
+      <c r="C32" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>46318</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="0" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="9"/>
+      <c r="C33" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>46322</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="0" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="9"/>
+      <c r="C34" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>46323</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="0" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="9"/>
+      <c r="C35" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="0" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="9"/>
+      <c r="C36" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="C22" s="5" t="n">
-        <v>46294</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="1" t="n">
+      <c r="D36" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>46325</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="0" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="10" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>46329</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="0" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="10"/>
+      <c r="C38" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>46330</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="0" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="10"/>
+      <c r="C39" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>46331</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="0" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="10"/>
+      <c r="C40" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>46332</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="0" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="10"/>
+      <c r="C41" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>46333</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="0" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="10"/>
+      <c r="C42" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E42" s="4" t="n">
+        <v>46334</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="0" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="10"/>
+      <c r="C43" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E43" s="4" t="n">
+        <v>46335</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="0" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="10"/>
+      <c r="C44" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E44" s="4" t="n">
+        <v>46336</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="0" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="10"/>
+      <c r="C45" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E45" s="4" t="n">
+        <v>46337</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="0" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="10"/>
+      <c r="C46" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="10"/>
-      <c r="C23" s="7" t="n">
-        <v>46295</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="10"/>
-      <c r="C24" s="7" t="n">
-        <v>46297</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="10"/>
-      <c r="C25" s="5" t="n">
-        <v>46301</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="10"/>
-      <c r="C26" s="7" t="n">
-        <v>46302</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="10"/>
-      <c r="C27" s="7" t="n">
-        <v>46304</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="10"/>
-      <c r="C28" s="5" t="n">
-        <v>46308</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="10"/>
-      <c r="C29" s="7" t="n">
-        <v>46309</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="10"/>
-      <c r="C30" s="5" t="n">
-        <v>46311</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="10"/>
-      <c r="C31" s="7" t="n">
-        <v>46315</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="10"/>
-      <c r="C32" s="5" t="n">
-        <v>46316</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="10"/>
-      <c r="C33" s="7" t="n">
-        <v>46318</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="10"/>
-      <c r="C34" s="5" t="n">
-        <v>46322</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="10"/>
-      <c r="C35" s="5" t="n">
-        <v>46323</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="10"/>
-      <c r="C36" s="5" t="n">
-        <v>46325</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="11" t="s">
+      <c r="D46" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>46350</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="0" t="n">
         <v>45</v>
       </c>
-      <c r="C37" s="5" t="n">
-        <v>46329</v>
-      </c>
-      <c r="D37" s="2" t="s">
+      <c r="B47" s="10"/>
+      <c r="E47" s="4" t="n">
+        <v>46351</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="0" t="n">
         <v>46</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="5" t="n">
-        <v>46330</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="11"/>
-      <c r="C39" s="5" t="n">
-        <v>46332</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" s="11"/>
-      <c r="C40" s="5" t="n">
-        <v>46336</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" s="11"/>
-      <c r="C41" s="5" t="n">
-        <v>46337</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="5" t="n">
-        <v>46339</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" s="11"/>
-      <c r="C43" s="5" t="n">
-        <v>46343</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" s="11"/>
-      <c r="C44" s="5" t="n">
-        <v>46344</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="5" t="n">
-        <v>46346</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="5" t="n">
-        <v>46350</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" s="11"/>
-      <c r="C47" s="5" t="n">
-        <v>46351</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="1" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" s="11"/>
-      <c r="C48" s="5" t="n">
+      <c r="B48" s="10"/>
+      <c r="C48" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E48" s="4" t="n">
         <v>46353</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
